--- a/AAII_Financials/Yearly/VRE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VRE_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
   <si>
     <t>VRE</t>
   </si>
@@ -656,147 +656,159 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>355000</v>
+        <v>279900</v>
       </c>
       <c r="E8" s="3">
-        <v>323400</v>
+        <v>233400</v>
       </c>
       <c r="F8" s="3">
+        <v>194600</v>
+      </c>
+      <c r="G8" s="3">
         <v>307500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>357200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>371700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>459000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>613400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>594900</v>
       </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>161300</v>
+        <v>122800</v>
       </c>
       <c r="E9" s="3">
-        <v>146000</v>
+        <v>111400</v>
       </c>
       <c r="F9" s="3">
+        <v>95400</v>
+      </c>
+      <c r="G9" s="3">
         <v>139800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>149000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>157700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>192600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>267200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>272200</v>
       </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>193700</v>
+        <v>157000</v>
       </c>
       <c r="E10" s="3">
-        <v>177400</v>
+        <v>122100</v>
       </c>
       <c r="F10" s="3">
+        <v>99200</v>
+      </c>
+      <c r="G10" s="3">
         <v>167600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>208200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>214000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>266500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>346200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>322700</v>
       </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -809,8 +821,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -838,9 +851,12 @@
       <c r="K12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -868,69 +884,78 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>107400</v>
+        <v>55100</v>
       </c>
       <c r="E14" s="3">
-        <v>98400</v>
+        <v>5300</v>
       </c>
       <c r="F14" s="3">
+        <v>97100</v>
+      </c>
+      <c r="G14" s="3">
         <v>21100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>29900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>33600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>30500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>197900</v>
       </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>111500</v>
+        <v>93600</v>
       </c>
       <c r="E15" s="3">
-        <v>110000</v>
+        <v>197000</v>
       </c>
       <c r="F15" s="3">
+        <v>178500</v>
+      </c>
+      <c r="G15" s="3">
         <v>120500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>133600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>113800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>142300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>186700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>170400</v>
       </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -940,68 +965,75 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>436400</v>
+        <v>316000</v>
       </c>
       <c r="E17" s="3">
-        <v>411600</v>
+        <v>265800</v>
       </c>
       <c r="F17" s="3">
+        <v>305800</v>
+      </c>
+      <c r="G17" s="3">
         <v>352400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>372300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>359000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>385800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>539300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>691200</v>
       </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-81400</v>
+        <v>-36100</v>
       </c>
       <c r="E18" s="3">
-        <v>-88200</v>
+        <v>-32300</v>
       </c>
       <c r="F18" s="3">
+        <v>-111200</v>
+      </c>
+      <c r="G18" s="3">
         <v>-44900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-15100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>12700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>73300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>74100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-96300</v>
       </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1014,133 +1046,146 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>125300</v>
+        <v>-31200</v>
       </c>
       <c r="E20" s="3">
+        <v>59200</v>
+      </c>
+      <c r="F20" s="3">
         <v>1400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>4700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>358500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>147700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>22100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>151100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>57300</v>
       </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>155300</v>
+        <v>26200</v>
       </c>
       <c r="E21" s="3">
-        <v>22000</v>
+        <v>138200</v>
       </c>
       <c r="F21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G21" s="3">
         <v>78100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>471500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>330700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>294000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>411700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>133100</v>
       </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>78000</v>
+        <v>89400</v>
       </c>
       <c r="E22" s="3">
-        <v>65200</v>
+        <v>66400</v>
       </c>
       <c r="F22" s="3">
+        <v>47500</v>
+      </c>
+      <c r="G22" s="3">
         <v>81000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>90600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>77600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>84500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>94900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>103100</v>
       </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-34100</v>
+        <v>-156700</v>
       </c>
       <c r="E23" s="3">
-        <v>-152000</v>
+        <v>-39500</v>
       </c>
       <c r="F23" s="3">
+        <v>-157300</v>
+      </c>
+      <c r="G23" s="3">
         <v>-121300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>252800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>82800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>10800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>130300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-142100</v>
       </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
@@ -1148,24 +1193,27 @@
       <c r="F24" s="3">
         <v>0</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="G24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1193,69 +1241,78 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-34100</v>
+        <v>-157200</v>
       </c>
       <c r="E26" s="3">
-        <v>-152000</v>
+        <v>-39500</v>
       </c>
       <c r="F26" s="3">
+        <v>-157300</v>
+      </c>
+      <c r="G26" s="3">
         <v>-121300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>252800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>82800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>10800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>130300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-142100</v>
       </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-56900</v>
+        <v>-152700</v>
       </c>
       <c r="E27" s="3">
-        <v>-164900</v>
+        <v>-61800</v>
       </c>
       <c r="F27" s="3">
+        <v>-169700</v>
+      </c>
+      <c r="G27" s="3">
         <v>-142500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>184500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>51500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-15300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>117200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-125800</v>
       </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1283,39 +1340,45 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>-700</v>
+        <v>41000</v>
       </c>
       <c r="E29" s="3">
-        <v>38600</v>
+        <v>4300</v>
       </c>
       <c r="F29" s="3">
+        <v>43400</v>
+      </c>
+      <c r="G29" s="3">
         <v>79300</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-98500</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>21200</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>20500</v>
       </c>
-      <c r="J29" s="3" t="s">
+      <c r="K29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1343,9 +1406,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1373,69 +1439,78 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-125300</v>
+        <v>31200</v>
       </c>
       <c r="E32" s="3">
+        <v>-59200</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-4700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-358500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-147700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-22100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-151100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-57300</v>
       </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-111800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-57500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-126300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-63200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>86000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>72700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>5200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>117200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-125800</v>
       </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1463,74 +1538,83 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-111800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-57500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-126300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-63200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>86000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>72700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>5200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>117200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-125800</v>
       </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1543,8 +1627,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1557,38 +1642,42 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E41" s="3">
         <v>26800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>31800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>38100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>25600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>29600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>28200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>31600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>37100</v>
       </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1616,39 +1705,45 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E43" s="3">
         <v>42700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>74600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>94300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>102900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>106100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>107600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>110700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>131000</v>
       </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1676,39 +1771,45 @@
       <c r="K44" s="3">
         <v>0</v>
       </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>33700</v>
+      </c>
+      <c r="E45" s="3">
         <v>43800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>28900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>36000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>73400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>97000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>80900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>60700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>49400</v>
       </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -1736,99 +1837,111 @@
       <c r="K46" s="3">
         <v>0</v>
       </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L46" s="3">
+        <v>0</v>
+      </c>
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>118000</v>
+      </c>
+      <c r="E47" s="3">
         <v>127500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>141800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>163500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>210700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>280200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>302800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>333300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>317000</v>
       </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3012500</v>
+      </c>
+      <c r="E48" s="3">
         <v>3611000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4134400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4661600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4687200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4317000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4187300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3512500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3343200</v>
       </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E49" s="3">
         <v>12300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>42200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>74600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>89000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>92800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>105700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>75000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>13900</v>
       </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1856,9 +1969,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1886,39 +2002,45 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E52" s="3">
         <v>56700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>73700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>79800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>104000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>127800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>137200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>170100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>299000</v>
       </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1946,39 +2068,45 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3241000</v>
+      </c>
+      <c r="E54" s="3">
         <v>3920800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4527300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5147800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5292800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5060600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4957900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4296800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4054000</v>
       </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1991,8 +2119,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2005,38 +2134,42 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>49300</v>
+      </c>
+      <c r="E57" s="3">
         <v>69100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>112700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>172400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>185700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>168100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>192700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>159900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>270100</v>
       </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2064,39 +2197,45 @@
       <c r="K58" s="3">
         <v>0</v>
       </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E59" s="3">
         <v>10100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>28400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>33800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>56300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>31000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>30700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>23800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>40100</v>
       </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2124,39 +2263,45 @@
       <c r="K60" s="3">
         <v>0</v>
       </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L60" s="3">
+        <v>0</v>
+      </c>
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1853900</v>
+      </c>
+      <c r="E61" s="3">
         <v>1904000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2389100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2801800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2808500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2792700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2809600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2340000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2145400</v>
       </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2184,9 +2329,12 @@
       <c r="K62" s="3">
         <v>0</v>
       </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L62" s="3">
+        <v>0</v>
+      </c>
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2214,9 +2362,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2244,9 +2395,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2274,39 +2428,45 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2103600</v>
+      </c>
+      <c r="E66" s="3">
         <v>2685100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3245300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3749000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3799100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3574000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3481600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2769600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2598300</v>
       </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2319,8 +2479,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2348,9 +2509,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2378,9 +2542,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2408,9 +2575,12 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2438,39 +2608,45 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1418300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1301400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1249300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1130300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1042600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1084500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1096400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1052200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1115600</v>
       </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2498,9 +2674,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2528,9 +2707,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2558,39 +2740,45 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1137500</v>
+      </c>
+      <c r="E76" s="3">
         <v>1235700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1282000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1398800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1493700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1486700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1476300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1527200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1455700</v>
       </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2618,74 +2806,83 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-111800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-57500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-126300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-63200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>86000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>72700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>5200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>117200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-125800</v>
       </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2698,38 +2895,42 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>93500</v>
+      </c>
+      <c r="E83" s="3">
         <v>111400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>108800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>118300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>128100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>170300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>198700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>186500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>172100</v>
       </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2757,9 +2958,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2787,9 +2991,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2817,9 +3024,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2847,9 +3057,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2877,39 +3090,45 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>45500</v>
+      </c>
+      <c r="E89" s="3">
         <v>66500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>56100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>85400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>131800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>167100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>196100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>100100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>169500</v>
       </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2922,38 +3141,42 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-20900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-255200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-276700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-451400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1225900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-518000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-977300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-736400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-245600</v>
       </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2981,9 +3204,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3011,39 +3237,45 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>579700</v>
+      </c>
+      <c r="E94" s="3">
         <v>220100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>446200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>28500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-416100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-168200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-564700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-138200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-222500</v>
       </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3056,38 +3288,42 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E96" s="3">
         <v>-100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-60500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-102600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-94000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-77800</v>
-      </c>
-      <c r="J96" s="3">
-        <v>-60000</v>
       </c>
       <c r="K96" s="3">
         <v>-60000</v>
       </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>-60000</v>
+      </c>
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3115,9 +3351,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3145,9 +3384,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3175,39 +3417,45 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-618300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-290300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-503200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-102800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>275800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-17300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>351000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>51200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>60600</v>
       </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3235,37 +3483,43 @@
       <c r="K101" s="3">
         <v>0</v>
       </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>11100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-8400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-18400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-17600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>13100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>7500</v>
       </c>
-      <c r="L102" s="3"/>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/VRE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VRE_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="92">
   <si>
     <t>VRE</t>
   </si>
@@ -714,25 +714,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>279900</v>
+        <v>283600</v>
       </c>
       <c r="E8" s="3">
-        <v>233400</v>
+        <v>234800</v>
       </c>
       <c r="F8" s="3">
-        <v>194600</v>
+        <v>190500</v>
       </c>
       <c r="G8" s="3">
-        <v>307500</v>
+        <v>303800</v>
       </c>
       <c r="H8" s="3">
-        <v>357200</v>
+        <v>355900</v>
       </c>
       <c r="I8" s="3">
-        <v>371700</v>
+        <v>371600</v>
       </c>
       <c r="J8" s="3">
-        <v>459000</v>
+        <v>453700</v>
       </c>
       <c r="K8" s="3">
         <v>613400</v>
@@ -780,25 +780,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>157000</v>
+        <v>160700</v>
       </c>
       <c r="E10" s="3">
-        <v>122100</v>
+        <v>123400</v>
       </c>
       <c r="F10" s="3">
-        <v>99200</v>
+        <v>95100</v>
       </c>
       <c r="G10" s="3">
-        <v>167600</v>
+        <v>163900</v>
       </c>
       <c r="H10" s="3">
-        <v>208200</v>
+        <v>206900</v>
       </c>
       <c r="I10" s="3">
-        <v>214000</v>
+        <v>213900</v>
       </c>
       <c r="J10" s="3">
-        <v>266500</v>
+        <v>261200</v>
       </c>
       <c r="K10" s="3">
         <v>346200</v>
@@ -894,25 +894,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>55100</v>
+        <v>38100</v>
       </c>
       <c r="E14" s="3">
-        <v>5300</v>
+        <v>-47600</v>
       </c>
       <c r="F14" s="3">
-        <v>97100</v>
+        <v>67700</v>
       </c>
       <c r="G14" s="3">
-        <v>21100</v>
+        <v>20300</v>
       </c>
       <c r="H14" s="3">
-        <v>29900</v>
+        <v>-326200</v>
       </c>
       <c r="I14" s="3">
-        <v>33600</v>
+        <v>-104400</v>
       </c>
       <c r="J14" s="3">
-        <v>400</v>
+        <v>-24300</v>
       </c>
       <c r="K14" s="3">
         <v>30500</v>
@@ -930,10 +930,10 @@
         <v>93600</v>
       </c>
       <c r="E15" s="3">
-        <v>197000</v>
+        <v>85400</v>
       </c>
       <c r="F15" s="3">
-        <v>178500</v>
+        <v>68500</v>
       </c>
       <c r="G15" s="3">
         <v>120500</v>
@@ -972,25 +972,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>316000</v>
+        <v>260900</v>
       </c>
       <c r="E17" s="3">
-        <v>265800</v>
+        <v>252800</v>
       </c>
       <c r="F17" s="3">
-        <v>305800</v>
+        <v>220900</v>
       </c>
       <c r="G17" s="3">
-        <v>352400</v>
+        <v>321300</v>
       </c>
       <c r="H17" s="3">
-        <v>372300</v>
+        <v>341100</v>
       </c>
       <c r="I17" s="3">
-        <v>359000</v>
+        <v>318800</v>
       </c>
       <c r="J17" s="3">
-        <v>385800</v>
+        <v>385400</v>
       </c>
       <c r="K17" s="3">
         <v>539300</v>
@@ -1005,25 +1005,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-36100</v>
+        <v>22700</v>
       </c>
       <c r="E18" s="3">
-        <v>-32300</v>
+        <v>-18000</v>
       </c>
       <c r="F18" s="3">
-        <v>-111200</v>
+        <v>-30400</v>
       </c>
       <c r="G18" s="3">
-        <v>-44900</v>
+        <v>-17500</v>
       </c>
       <c r="H18" s="3">
-        <v>-15100</v>
+        <v>14800</v>
       </c>
       <c r="I18" s="3">
-        <v>12700</v>
+        <v>52800</v>
       </c>
       <c r="J18" s="3">
-        <v>73300</v>
+        <v>68400</v>
       </c>
       <c r="K18" s="3">
         <v>74100</v>
@@ -1053,25 +1053,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-31200</v>
+        <v>7600</v>
       </c>
       <c r="E20" s="3">
-        <v>59200</v>
+        <v>3500</v>
       </c>
       <c r="F20" s="3">
-        <v>1400</v>
+        <v>12200</v>
       </c>
       <c r="G20" s="3">
-        <v>4700</v>
-      </c>
-      <c r="H20" s="3">
-        <v>358500</v>
-      </c>
-      <c r="I20" s="3">
-        <v>147700</v>
-      </c>
-      <c r="J20" s="3">
-        <v>22100</v>
+        <v>2600</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K20" s="3">
         <v>151100</v>
@@ -1086,25 +1086,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>26200</v>
+        <v>108600</v>
       </c>
       <c r="E21" s="3">
-        <v>138200</v>
+        <v>63900</v>
       </c>
       <c r="F21" s="3">
-        <v>-900</v>
+        <v>25900</v>
       </c>
       <c r="G21" s="3">
-        <v>78100</v>
+        <v>100400</v>
       </c>
       <c r="H21" s="3">
-        <v>471500</v>
+        <v>148400</v>
       </c>
       <c r="I21" s="3">
-        <v>330700</v>
+        <v>166600</v>
       </c>
       <c r="J21" s="3">
-        <v>294000</v>
+        <v>210700</v>
       </c>
       <c r="K21" s="3">
         <v>411700</v>
@@ -1119,7 +1119,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>89400</v>
+        <v>139100</v>
       </c>
       <c r="E22" s="3">
         <v>66400</v>
@@ -1164,7 +1164,7 @@
         <v>-121300</v>
       </c>
       <c r="H23" s="3">
-        <v>252800</v>
+        <v>252900</v>
       </c>
       <c r="I23" s="3">
         <v>82800</v>
@@ -1187,11 +1187,11 @@
       <c r="D24" s="3">
         <v>500</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
+      <c r="E24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>8</v>
@@ -1263,7 +1263,7 @@
         <v>-121300</v>
       </c>
       <c r="H26" s="3">
-        <v>252800</v>
+        <v>252900</v>
       </c>
       <c r="I26" s="3">
         <v>82800</v>
@@ -1284,25 +1284,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-152700</v>
+        <v>-111800</v>
       </c>
       <c r="E27" s="3">
-        <v>-61800</v>
+        <v>-57500</v>
       </c>
       <c r="F27" s="3">
-        <v>-169700</v>
+        <v>-126300</v>
       </c>
       <c r="G27" s="3">
-        <v>-142500</v>
+        <v>-63200</v>
       </c>
       <c r="H27" s="3">
-        <v>184500</v>
+        <v>86000</v>
       </c>
       <c r="I27" s="3">
-        <v>51500</v>
+        <v>72700</v>
       </c>
       <c r="J27" s="3">
-        <v>-15300</v>
+        <v>5200</v>
       </c>
       <c r="K27" s="3">
         <v>117200</v>
@@ -1362,7 +1362,7 @@
         <v>79300</v>
       </c>
       <c r="H29" s="3">
-        <v>-98500</v>
+        <v>-98600</v>
       </c>
       <c r="I29" s="3">
         <v>21200</v>
@@ -1449,25 +1449,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>31200</v>
+        <v>-7600</v>
       </c>
       <c r="E32" s="3">
-        <v>-59200</v>
+        <v>-3500</v>
       </c>
       <c r="F32" s="3">
-        <v>-1400</v>
+        <v>-12200</v>
       </c>
       <c r="G32" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-358500</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-147700</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-22100</v>
+        <v>-2600</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K32" s="3">
         <v>-151100</v>
@@ -1482,25 +1482,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-111800</v>
+        <v>-107300</v>
       </c>
       <c r="E33" s="3">
-        <v>-57500</v>
+        <v>-52100</v>
       </c>
       <c r="F33" s="3">
-        <v>-126300</v>
+        <v>-119000</v>
       </c>
       <c r="G33" s="3">
-        <v>-63200</v>
+        <v>-51400</v>
       </c>
       <c r="H33" s="3">
-        <v>86000</v>
+        <v>111900</v>
       </c>
       <c r="I33" s="3">
-        <v>72700</v>
+        <v>84100</v>
       </c>
       <c r="J33" s="3">
-        <v>5200</v>
+        <v>23200</v>
       </c>
       <c r="K33" s="3">
         <v>117200</v>
@@ -1548,25 +1548,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-111800</v>
+        <v>-107300</v>
       </c>
       <c r="E35" s="3">
-        <v>-57500</v>
+        <v>-52100</v>
       </c>
       <c r="F35" s="3">
-        <v>-126300</v>
+        <v>-119000</v>
       </c>
       <c r="G35" s="3">
-        <v>-63200</v>
+        <v>-51400</v>
       </c>
       <c r="H35" s="3">
-        <v>86000</v>
+        <v>111900</v>
       </c>
       <c r="I35" s="3">
-        <v>72700</v>
+        <v>84100</v>
       </c>
       <c r="J35" s="3">
-        <v>5200</v>
+        <v>23200</v>
       </c>
       <c r="K35" s="3">
         <v>117200</v>
@@ -1697,10 +1697,10 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>10200</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -1715,25 +1715,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>8200</v>
+        <v>8300</v>
       </c>
       <c r="E43" s="3">
-        <v>42700</v>
+        <v>44000</v>
       </c>
       <c r="F43" s="3">
-        <v>74600</v>
+        <v>78700</v>
       </c>
       <c r="G43" s="3">
-        <v>94300</v>
+        <v>95500</v>
       </c>
       <c r="H43" s="3">
-        <v>102900</v>
+        <v>132600</v>
       </c>
       <c r="I43" s="3">
-        <v>106100</v>
+        <v>157500</v>
       </c>
       <c r="J43" s="3">
-        <v>107600</v>
+        <v>139000</v>
       </c>
       <c r="K43" s="3">
         <v>110700</v>
@@ -1747,26 +1747,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -1781,25 +1781,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>33700</v>
+        <v>92300</v>
       </c>
       <c r="E45" s="3">
-        <v>43800</v>
+        <v>237700</v>
       </c>
       <c r="F45" s="3">
-        <v>28900</v>
+        <v>647500</v>
       </c>
       <c r="G45" s="3">
-        <v>36000</v>
+        <v>692900</v>
       </c>
       <c r="H45" s="3">
-        <v>73400</v>
+        <v>1011800</v>
       </c>
       <c r="I45" s="3">
-        <v>97000</v>
+        <v>156600</v>
       </c>
       <c r="J45" s="3">
-        <v>80900</v>
+        <v>217600</v>
       </c>
       <c r="K45" s="3">
         <v>60700</v>
@@ -1814,25 +1814,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>155200</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>329300</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>777600</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>840700</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>1185500</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>373900</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>432600</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -1850,22 +1850,22 @@
         <v>118000</v>
       </c>
       <c r="E47" s="3">
-        <v>127500</v>
+        <v>126200</v>
       </c>
       <c r="F47" s="3">
-        <v>141800</v>
+        <v>137800</v>
       </c>
       <c r="G47" s="3">
-        <v>163500</v>
+        <v>162400</v>
       </c>
       <c r="H47" s="3">
-        <v>210700</v>
+        <v>209100</v>
       </c>
       <c r="I47" s="3">
-        <v>280200</v>
+        <v>232800</v>
       </c>
       <c r="J47" s="3">
-        <v>302800</v>
+        <v>252600</v>
       </c>
       <c r="K47" s="3">
         <v>333300</v>
@@ -1880,25 +1880,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3012500</v>
+        <v>2953900</v>
       </c>
       <c r="E48" s="3">
-        <v>3611000</v>
+        <v>3417100</v>
       </c>
       <c r="F48" s="3">
-        <v>4134400</v>
+        <v>3515700</v>
       </c>
       <c r="G48" s="3">
-        <v>4661600</v>
+        <v>4004600</v>
       </c>
       <c r="H48" s="3">
-        <v>4687200</v>
+        <v>3720700</v>
       </c>
       <c r="I48" s="3">
-        <v>4317000</v>
+        <v>4208100</v>
       </c>
       <c r="J48" s="3">
-        <v>4187300</v>
+        <v>4015800</v>
       </c>
       <c r="K48" s="3">
         <v>3512500</v>
@@ -2011,26 +2011,26 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>30600</v>
-      </c>
-      <c r="E52" s="3">
-        <v>56700</v>
-      </c>
-      <c r="F52" s="3">
-        <v>73700</v>
-      </c>
-      <c r="G52" s="3">
-        <v>79800</v>
-      </c>
-      <c r="H52" s="3">
-        <v>104000</v>
-      </c>
-      <c r="I52" s="3">
-        <v>127800</v>
-      </c>
-      <c r="J52" s="3">
-        <v>137200</v>
+      <c r="D52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K52" s="3">
         <v>170100</v>
@@ -2141,25 +2141,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>49300</v>
+        <v>48100</v>
       </c>
       <c r="E57" s="3">
-        <v>69100</v>
+        <v>68800</v>
       </c>
       <c r="F57" s="3">
-        <v>112700</v>
+        <v>111300</v>
       </c>
       <c r="G57" s="3">
-        <v>172400</v>
+        <v>171100</v>
       </c>
       <c r="H57" s="3">
-        <v>185700</v>
+        <v>185800</v>
       </c>
       <c r="I57" s="3">
-        <v>168100</v>
+        <v>165800</v>
       </c>
       <c r="J57" s="3">
-        <v>192700</v>
+        <v>188100</v>
       </c>
       <c r="K57" s="3">
         <v>159900</v>
@@ -2174,19 +2174,19 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>309300</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>180400</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
@@ -2207,25 +2207,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>18300</v>
+        <v>5500</v>
       </c>
       <c r="E59" s="3">
-        <v>10100</v>
+        <v>100</v>
       </c>
       <c r="F59" s="3">
-        <v>28400</v>
+        <v>400</v>
       </c>
       <c r="G59" s="3">
-        <v>33800</v>
+        <v>1500</v>
       </c>
       <c r="H59" s="3">
-        <v>56300</v>
+        <v>22300</v>
       </c>
       <c r="I59" s="3">
-        <v>31000</v>
+        <v>24200</v>
       </c>
       <c r="J59" s="3">
-        <v>30700</v>
+        <v>25800</v>
       </c>
       <c r="K59" s="3">
         <v>23800</v>
@@ -2240,25 +2240,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>369500</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>256500</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>119100</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>184400</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>220000</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>199100</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>223400</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -2273,19 +2273,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1853900</v>
+        <v>1552000</v>
       </c>
       <c r="E61" s="3">
-        <v>1904000</v>
+        <v>1726800</v>
       </c>
       <c r="F61" s="3">
-        <v>2389100</v>
+        <v>2411100</v>
       </c>
       <c r="G61" s="3">
-        <v>2801800</v>
+        <v>2823600</v>
       </c>
       <c r="H61" s="3">
-        <v>2808500</v>
+        <v>2830500</v>
       </c>
       <c r="I61" s="3">
         <v>2792700</v>
@@ -2305,26 +2305,26 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -2438,25 +2438,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>2103600</v>
+        <v>1936500</v>
       </c>
       <c r="E66" s="3">
-        <v>2685100</v>
+        <v>2006200</v>
       </c>
       <c r="F66" s="3">
-        <v>3245300</v>
+        <v>2556600</v>
       </c>
       <c r="G66" s="3">
-        <v>3749000</v>
+        <v>3042100</v>
       </c>
       <c r="H66" s="3">
-        <v>3799100</v>
+        <v>3089900</v>
       </c>
       <c r="I66" s="3">
-        <v>3574000</v>
+        <v>3033000</v>
       </c>
       <c r="J66" s="3">
-        <v>3481600</v>
+        <v>3077000</v>
       </c>
       <c r="K66" s="3">
         <v>2769600</v>
@@ -2617,26 +2617,26 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>-1418300</v>
-      </c>
-      <c r="E72" s="3">
-        <v>-1301400</v>
-      </c>
-      <c r="F72" s="3">
-        <v>-1249300</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-1130300</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-1042600</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-1084500</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-1096400</v>
+      <c r="D72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K72" s="3">
         <v>-1052200</v>
@@ -2854,25 +2854,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-111800</v>
+        <v>-107300</v>
       </c>
       <c r="E81" s="3">
-        <v>-57500</v>
+        <v>-52100</v>
       </c>
       <c r="F81" s="3">
-        <v>-126300</v>
+        <v>-119000</v>
       </c>
       <c r="G81" s="3">
-        <v>-63200</v>
+        <v>-51400</v>
       </c>
       <c r="H81" s="3">
-        <v>86000</v>
+        <v>111900</v>
       </c>
       <c r="I81" s="3">
-        <v>72700</v>
+        <v>84100</v>
       </c>
       <c r="J81" s="3">
-        <v>5200</v>
+        <v>23200</v>
       </c>
       <c r="K81" s="3">
         <v>117200</v>
@@ -2905,22 +2905,22 @@
         <v>93500</v>
       </c>
       <c r="E83" s="3">
-        <v>111400</v>
+        <v>85400</v>
       </c>
       <c r="F83" s="3">
-        <v>108800</v>
+        <v>68500</v>
       </c>
       <c r="G83" s="3">
-        <v>118300</v>
+        <v>117700</v>
       </c>
       <c r="H83" s="3">
-        <v>128100</v>
+        <v>129700</v>
       </c>
       <c r="I83" s="3">
-        <v>170300</v>
+        <v>109400</v>
       </c>
       <c r="J83" s="3">
-        <v>198700</v>
+        <v>135900</v>
       </c>
       <c r="K83" s="3">
         <v>186500</v>
@@ -3147,26 +3147,26 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-20900</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-255200</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-276700</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-451400</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-1225900</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-518000</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-977300</v>
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K91" s="3">
         <v>-736400</v>
@@ -3295,25 +3295,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-5100</v>
+        <v>5100</v>
       </c>
       <c r="E96" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F96" s="3">
-        <v>-500</v>
+        <v>500</v>
       </c>
       <c r="G96" s="3">
-        <v>-60500</v>
+        <v>60500</v>
       </c>
       <c r="H96" s="3">
-        <v>-102600</v>
+        <v>80700</v>
       </c>
       <c r="I96" s="3">
-        <v>-94000</v>
+        <v>80600</v>
       </c>
       <c r="J96" s="3">
-        <v>-77800</v>
+        <v>77800</v>
       </c>
       <c r="K96" s="3">
         <v>-60000</v>
@@ -3459,26 +3459,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>

--- a/AAII_Financials/Yearly/VRE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VRE_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
   <si>
     <t>VRE</t>
   </si>
@@ -656,159 +656,171 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>283600</v>
+        <v>275600</v>
       </c>
       <c r="E8" s="3">
-        <v>234800</v>
+        <v>264000</v>
       </c>
       <c r="F8" s="3">
+        <v>214700</v>
+      </c>
+      <c r="G8" s="3">
         <v>190500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>303800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>355900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>371600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>453700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>613400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>594900</v>
       </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>122800</v>
+        <v>111100</v>
       </c>
       <c r="E9" s="3">
-        <v>111400</v>
+        <v>107300</v>
       </c>
       <c r="F9" s="3">
+        <v>98800</v>
+      </c>
+      <c r="G9" s="3">
         <v>95400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>139800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>149000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>157700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>192600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>267200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>272200</v>
       </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>160700</v>
+        <v>164600</v>
       </c>
       <c r="E10" s="3">
-        <v>123400</v>
+        <v>156700</v>
       </c>
       <c r="F10" s="3">
+        <v>115900</v>
+      </c>
+      <c r="G10" s="3">
         <v>95100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>163900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>206900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>213900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>261200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>346200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>322700</v>
       </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -822,8 +834,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -854,9 +867,12 @@
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -887,75 +903,84 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>38100</v>
+        <v>-14400</v>
       </c>
       <c r="E14" s="3">
+        <v>5600</v>
+      </c>
+      <c r="F14" s="3">
         <v>-47600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>67700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>20300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-326200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-104400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-24300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>30500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>197900</v>
       </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>93600</v>
+        <v>82800</v>
       </c>
       <c r="E15" s="3">
-        <v>85400</v>
+        <v>86200</v>
       </c>
       <c r="F15" s="3">
+        <v>77900</v>
+      </c>
+      <c r="G15" s="3">
         <v>68500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>120500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>133600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>113800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>142300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>186700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>170400</v>
       </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -966,74 +991,81 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>260900</v>
+        <v>232900</v>
       </c>
       <c r="E17" s="3">
-        <v>252800</v>
+        <v>238000</v>
       </c>
       <c r="F17" s="3">
+        <v>232600</v>
+      </c>
+      <c r="G17" s="3">
         <v>220900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>321300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>341100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>318800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>385400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>539300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>691200</v>
       </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>22700</v>
+        <v>42700</v>
       </c>
       <c r="E18" s="3">
-        <v>-18000</v>
+        <v>26000</v>
       </c>
       <c r="F18" s="3">
+        <v>-17900</v>
+      </c>
+      <c r="G18" s="3">
         <v>-30400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-17500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>14800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>52800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>68400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>74100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-96300</v>
       </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1047,149 +1079,162 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E20" s="3">
         <v>7600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>12200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2600</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I20" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3">
         <v>151100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>57300</v>
       </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>108600</v>
+        <v>123200</v>
       </c>
       <c r="E21" s="3">
-        <v>63900</v>
+        <v>104600</v>
       </c>
       <c r="F21" s="3">
+        <v>56600</v>
+      </c>
+      <c r="G21" s="3">
         <v>25900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>100400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>148400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>166600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>210700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>411700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>133100</v>
       </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>88000</v>
+      </c>
+      <c r="E22" s="3">
         <v>139100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>66400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>47500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>81000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>90600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>77600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>84500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>94900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>103100</v>
       </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-156700</v>
+        <v>-30700</v>
       </c>
       <c r="E23" s="3">
-        <v>-39500</v>
+        <v>-120900</v>
       </c>
       <c r="F23" s="3">
+        <v>-39400</v>
+      </c>
+      <c r="G23" s="3">
         <v>-157300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-121300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>252900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>82800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>10800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>130300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-142100</v>
       </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>300</v>
+      </c>
+      <c r="E24" s="3">
         <v>500</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F24" s="3" t="s">
         <v>8</v>
       </c>
@@ -1205,15 +1250,18 @@
       <c r="J24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1244,75 +1292,84 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-157200</v>
+        <v>-31000</v>
       </c>
       <c r="E26" s="3">
-        <v>-39500</v>
+        <v>-121400</v>
       </c>
       <c r="F26" s="3">
+        <v>-39400</v>
+      </c>
+      <c r="G26" s="3">
         <v>-157300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-121300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>252900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>82800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>10800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>130300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-142100</v>
       </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-23100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-111800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-57500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-126300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-63200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>86000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>72700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>5200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>117200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-125800</v>
       </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1343,42 +1400,48 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>41000</v>
+        <v>3900</v>
       </c>
       <c r="E29" s="3">
-        <v>4300</v>
+        <v>8200</v>
       </c>
       <c r="F29" s="3">
+        <v>4100</v>
+      </c>
+      <c r="G29" s="3">
         <v>43400</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>79300</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-98600</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>21200</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>20500</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="L29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1409,9 +1472,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1442,75 +1508,84 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-7600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-12200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2600</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I32" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="3">
         <v>-151100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-57300</v>
       </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-23100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-107300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-52100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-119000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-51400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>111900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>84100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>23200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>117200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-125800</v>
       </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1541,80 +1616,89 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-23100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-107300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-52100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-119000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-51400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>111900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>84100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>23200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>117200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-125800</v>
       </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1628,8 +1712,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1643,41 +1728,45 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E41" s="3">
         <v>28000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>26800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>31800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>38100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>25600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>29600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>28200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>31600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>37100</v>
       </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1697,53 +1786,59 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>10200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>8100</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>8300</v>
+        <v>3600</v>
       </c>
       <c r="E43" s="3">
+        <v>8200</v>
+      </c>
+      <c r="F43" s="3">
         <v>44000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>78700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>95500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>132600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>157500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>139000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>110700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>131000</v>
       </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1768,180 +1863,198 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
       </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>34600</v>
+      </c>
+      <c r="E45" s="3">
         <v>92300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>237700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>647500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>692900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1011800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>156600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>217600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>60700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>49400</v>
       </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>62500</v>
+      </c>
+      <c r="E46" s="3">
         <v>155200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>329300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>777600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>840700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1185500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>373900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>432600</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M46" s="3">
+        <v>0</v>
+      </c>
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>111300</v>
+      </c>
+      <c r="E47" s="3">
         <v>118000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>126200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>137800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>162400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>209100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>232800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>252600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>333300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>317000</v>
       </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2792900</v>
+      </c>
+      <c r="E48" s="3">
         <v>2953900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3417100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3515700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4004600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3720700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4208100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4015800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3512500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3343200</v>
       </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E49" s="3">
         <v>10000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>12300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>42200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>74600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>89000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>92800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>105700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>75000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>13900</v>
       </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1972,9 +2085,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2005,9 +2121,12 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2032,15 +2151,18 @@
       <c r="J52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L52" s="3">
         <v>170100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>299000</v>
       </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2071,42 +2193,48 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2982700</v>
+      </c>
+      <c r="E54" s="3">
         <v>3241000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3920800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4527300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5147800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5292800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5060600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4957900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4296800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4054000</v>
       </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2120,8 +2248,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2135,61 +2264,65 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>36200</v>
+      </c>
+      <c r="E57" s="3">
         <v>48100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>68800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>111300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>171100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>185800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>165800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>188100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>159900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>270100</v>
       </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E58" s="3">
         <v>309300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>180400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1700</v>
-      </c>
-      <c r="G58" s="3">
-        <v>1800</v>
       </c>
       <c r="H58" s="3">
         <v>1800</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="J58" s="3">
         <v>0</v>
@@ -2200,108 +2333,120 @@
       <c r="L58" s="3">
         <v>0</v>
       </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E59" s="3">
         <v>5500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>22300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>24200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>25800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>23800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>40100</v>
       </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>51300</v>
+      </c>
+      <c r="E60" s="3">
         <v>369500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>256500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>119100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>184400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>220000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>199100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>223400</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M60" s="3">
+        <v>0</v>
+      </c>
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1677600</v>
+      </c>
+      <c r="E61" s="3">
         <v>1552000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1726800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2411100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2823600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2830500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2792700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2809600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2340000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2145400</v>
       </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2326,15 +2471,18 @@
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M62" s="3">
+        <v>0</v>
+      </c>
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2365,9 +2513,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2398,9 +2549,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2431,42 +2585,48 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1740400</v>
+      </c>
+      <c r="E66" s="3">
         <v>1936500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2006200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2556600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3042100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3089900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3033000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3077000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2769600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2598300</v>
       </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2480,8 +2640,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2512,9 +2673,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2545,9 +2709,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2578,9 +2745,12 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2611,9 +2781,12 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -2638,15 +2811,18 @@
       <c r="J72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L72" s="3">
         <v>-1052200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1115600</v>
       </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2677,9 +2853,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2710,9 +2889,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2743,42 +2925,48 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1099400</v>
+      </c>
+      <c r="E76" s="3">
         <v>1137500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1235700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1282000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1398800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1493700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1486700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1476300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1527200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1455700</v>
       </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2809,80 +2997,89 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-23100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-107300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-52100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-119000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-51400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>111900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>84100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>23200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>117200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-125800</v>
       </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2896,41 +3093,45 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>93500</v>
+        <v>82700</v>
       </c>
       <c r="E83" s="3">
-        <v>85400</v>
+        <v>86200</v>
       </c>
       <c r="F83" s="3">
+        <v>77900</v>
+      </c>
+      <c r="G83" s="3">
         <v>68500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>117700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>129700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>109400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>135900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>186500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>172100</v>
       </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2961,9 +3162,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2994,9 +3198,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3027,9 +3234,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3060,9 +3270,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3093,42 +3306,48 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>52300</v>
+      </c>
+      <c r="E89" s="3">
         <v>45500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>66500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>56100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>85400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>131800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>167100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>196100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>100100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>169500</v>
       </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3142,8 +3361,9 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3168,15 +3388,18 @@
       <c r="J91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K91" s="3">
+      <c r="K91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L91" s="3">
         <v>-736400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-245600</v>
       </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3207,9 +3430,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3240,42 +3466,48 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>162100</v>
+      </c>
+      <c r="E94" s="3">
         <v>579700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>220100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>446200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>28500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-416100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-168200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-564700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-138200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-222500</v>
       </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3289,41 +3521,45 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E96" s="3">
         <v>5100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>60500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>80700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>80600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>77800</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-60000</v>
       </c>
       <c r="L96" s="3">
         <v>-60000</v>
       </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>-60000</v>
+      </c>
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3354,9 +3590,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3387,9 +3626,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3420,42 +3662,48 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-244600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-618300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-290300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-503200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-102800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>275800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-17300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>351000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>51200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>60600</v>
       </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3480,46 +3728,52 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
       </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-30300</v>
+      </c>
+      <c r="E102" s="3">
         <v>6900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>11100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-8400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-18400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-17600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>13100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>7500</v>
       </c>
-      <c r="M102" s="3"/>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/VRE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VRE_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
   <si>
     <t>VRE</t>
   </si>
@@ -656,171 +656,183 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>275600</v>
+        <v>293300</v>
       </c>
       <c r="E8" s="3">
-        <v>264000</v>
+        <v>274400</v>
       </c>
       <c r="F8" s="3">
-        <v>214700</v>
+        <v>262800</v>
       </c>
       <c r="G8" s="3">
+        <v>214400</v>
+      </c>
+      <c r="H8" s="3">
         <v>190500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>303800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>355900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>371600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>453700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>613400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>594900</v>
       </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>112300</v>
+      </c>
+      <c r="E9" s="3">
         <v>111100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>107300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>98800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>95400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>139800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>149000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>157700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>192600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>267200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>272200</v>
       </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>164600</v>
+        <v>181000</v>
       </c>
       <c r="E10" s="3">
-        <v>156700</v>
+        <v>163300</v>
       </c>
       <c r="F10" s="3">
-        <v>115900</v>
+        <v>155500</v>
       </c>
       <c r="G10" s="3">
+        <v>115600</v>
+      </c>
+      <c r="H10" s="3">
         <v>95100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>163900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>206900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>213900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>261200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>346200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>322700</v>
       </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -835,8 +847,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -870,9 +883,12 @@
       <c r="M12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -906,81 +922,90 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-14400</v>
+        <v>-107000</v>
       </c>
       <c r="E14" s="3">
-        <v>5600</v>
+        <v>-15700</v>
       </c>
       <c r="F14" s="3">
-        <v>-47600</v>
+        <v>4400</v>
       </c>
       <c r="G14" s="3">
+        <v>-47900</v>
+      </c>
+      <c r="H14" s="3">
         <v>67700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>20300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-326200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-104400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-24300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>30500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>197900</v>
       </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>86300</v>
+      </c>
+      <c r="E15" s="3">
         <v>82800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>86200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>77900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>68500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>120500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>133600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>113800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>142300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>186700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>170400</v>
       </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -992,80 +1017,87 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>235300</v>
+      </c>
+      <c r="E17" s="3">
         <v>232900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>238000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>232600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>220900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>321300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>341100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>318800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>385400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>539300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>691200</v>
       </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>42700</v>
+        <v>58000</v>
       </c>
       <c r="E18" s="3">
-        <v>26000</v>
+        <v>41500</v>
       </c>
       <c r="F18" s="3">
-        <v>-17900</v>
+        <v>24800</v>
       </c>
       <c r="G18" s="3">
+        <v>-18200</v>
+      </c>
+      <c r="H18" s="3">
         <v>-30400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-17500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>14800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>52800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>68400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>74100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-96300</v>
       </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1080,164 +1112,177 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E20" s="3">
         <v>2300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>7600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>12200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2600</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="3">
         <v>151100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>57300</v>
       </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>123200</v>
+        <v>142600</v>
       </c>
       <c r="E21" s="3">
-        <v>104600</v>
+        <v>122000</v>
       </c>
       <c r="F21" s="3">
-        <v>56600</v>
+        <v>103400</v>
       </c>
       <c r="G21" s="3">
+        <v>56300</v>
+      </c>
+      <c r="H21" s="3">
         <v>25900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>100400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>148400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>166600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>210700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>411700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>133100</v>
       </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>88600</v>
+      </c>
+      <c r="E22" s="3">
         <v>88000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>139100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>66400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>47500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>81000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>90600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>77600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>84500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>94900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>103100</v>
       </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>75100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-30700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-120900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-39400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-157300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-121300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>252900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>82800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>10800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>130300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-142100</v>
       </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>200</v>
+      </c>
+      <c r="E24" s="3">
         <v>300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>500</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G24" s="3" t="s">
         <v>8</v>
       </c>
@@ -1253,15 +1298,18 @@
       <c r="K24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1295,81 +1343,90 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>74800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-31000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-121400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-39400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-157300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-121300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>252900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>82800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>10800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>130300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-142100</v>
       </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>75200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-23100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-111800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-57500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-126300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-63200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>86000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>72700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>117200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-125800</v>
       </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1403,45 +1460,51 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E29" s="3">
         <v>3900</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>8200</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>4100</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>43400</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>79300</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-98600</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>21200</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>20500</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="M29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1475,9 +1538,12 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1511,81 +1577,90 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-7600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-12200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2600</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M32" s="3">
         <v>-151100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-57300</v>
       </c>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>75200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-23100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-107300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-52100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-119000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-51400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>111900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>84100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>23200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>117200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-125800</v>
       </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1619,86 +1694,95 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>75200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-23100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-107300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-52100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-119000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-51400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>111900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>84100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>23200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>117200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-125800</v>
       </c>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1713,8 +1797,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1729,44 +1814,48 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E41" s="3">
         <v>7300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>28000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>26800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>31800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>38100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>25600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>29600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>28200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>31600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>37100</v>
       </c>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1789,56 +1878,62 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>10200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>8100</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E43" s="3">
         <v>3600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>44000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>78700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>95500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>132600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>157500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>139000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>110700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>131000</v>
       </c>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1866,195 +1961,213 @@
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
       </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E45" s="3">
         <v>34600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>92300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>237700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>647500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>692900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1011800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>156600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>217600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>60700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>49400</v>
       </c>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>55400</v>
+      </c>
+      <c r="E46" s="3">
         <v>62500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>155200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>329300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>777600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>840700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1185500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>373900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>432600</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N46" s="3">
+        <v>0</v>
+      </c>
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>52200</v>
+      </c>
+      <c r="E47" s="3">
         <v>111300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>118000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>126200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>137800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>162400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>209100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>232800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>252600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>333300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>317000</v>
       </c>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2584300</v>
+      </c>
+      <c r="E48" s="3">
         <v>2792900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2953900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3417100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3515700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4004600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3720700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4208100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4015800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3512500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3343200</v>
       </c>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3"/>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E49" s="3">
         <v>9500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>12300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>42200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>74600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>89000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>92800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>105700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>75000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>13900</v>
       </c>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3"/>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2088,9 +2201,12 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3"/>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2124,9 +2240,12 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2154,15 +2273,18 @@
       <c r="K52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M52" s="3">
         <v>170100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>299000</v>
       </c>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2196,45 +2318,51 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3"/>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2706900</v>
+      </c>
+      <c r="E54" s="3">
         <v>2982700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3241000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3920800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4527300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5147800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5292800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5060600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4957900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4296800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4054000</v>
       </c>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3"/>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2249,8 +2377,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2265,67 +2394,71 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>38900</v>
+      </c>
+      <c r="E57" s="3">
         <v>36200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>48100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>68800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>111300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>171100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>185800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>165800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>188100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>159900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>270100</v>
       </c>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3"/>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>414500</v>
+      </c>
+      <c r="E58" s="3">
         <v>1300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>309300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>180400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1700</v>
-      </c>
-      <c r="H58" s="3">
-        <v>1800</v>
       </c>
       <c r="I58" s="3">
         <v>1800</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2336,117 +2469,129 @@
       <c r="M58" s="3">
         <v>0</v>
       </c>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3"/>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E59" s="3">
         <v>8500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>22300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>24200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>25800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>23800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>40100</v>
       </c>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3"/>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>467200</v>
+      </c>
+      <c r="E60" s="3">
         <v>51300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>369500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>256500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>119100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>184400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>220000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>199100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>223400</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
-      <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N60" s="3">
+        <v>0</v>
+      </c>
+      <c r="O60" s="3"/>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>953300</v>
+      </c>
+      <c r="E61" s="3">
         <v>1677600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1552000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1726800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2411100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2823600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2830500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2792700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2809600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2340000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2145400</v>
       </c>
-      <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2474,15 +2619,18 @@
       <c r="K62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="L62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
-      <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N62" s="3">
+        <v>0</v>
+      </c>
+      <c r="O62" s="3"/>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2516,9 +2664,12 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3"/>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2552,9 +2703,12 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2588,45 +2742,51 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1431900</v>
+      </c>
+      <c r="E66" s="3">
         <v>1740400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1936500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2006200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2556600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3042100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3089900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3033000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3077000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2769600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2598300</v>
       </c>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2641,8 +2801,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2676,9 +2837,12 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2712,9 +2876,12 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2748,9 +2915,12 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2784,9 +2954,12 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -2814,15 +2987,18 @@
       <c r="K72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M72" s="3">
         <v>-1052200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1115600</v>
       </c>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2856,9 +3032,12 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2892,9 +3071,12 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2928,45 +3110,51 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1151600</v>
+      </c>
+      <c r="E76" s="3">
         <v>1099400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1137500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1235700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1282000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1398800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1493700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1486700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1476300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1527200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1455700</v>
       </c>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3000,86 +3188,95 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3"/>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2"/>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>75200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-23100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-107300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-52100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-119000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-51400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>111900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>84100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>23200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>117200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-125800</v>
       </c>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3"/>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3094,44 +3291,48 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>86200</v>
+      </c>
+      <c r="E83" s="3">
         <v>82700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>86200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>77900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>68500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>117700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>129700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>109400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>135900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>186500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>172100</v>
       </c>
-      <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3"/>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3165,9 +3366,12 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3"/>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3201,9 +3405,12 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3"/>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3237,9 +3444,12 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3273,9 +3483,12 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3309,45 +3522,51 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>76000</v>
+      </c>
+      <c r="E89" s="3">
         <v>52300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>45500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>66500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>56100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>85400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>131800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>167100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>196100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>100100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>169500</v>
       </c>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3362,8 +3581,9 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3391,15 +3611,18 @@
       <c r="K91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L91" s="3">
+      <c r="L91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M91" s="3">
         <v>-736400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-245600</v>
       </c>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3433,9 +3656,12 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3"/>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3469,45 +3695,51 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>445400</v>
+      </c>
+      <c r="E94" s="3">
         <v>162100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>579700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>220100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>446200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>28500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-416100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-168200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-564700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-138200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-222500</v>
       </c>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3522,44 +3754,48 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E96" s="3">
         <v>24100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>5100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>60500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>80700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>80600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>77800</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-60000</v>
       </c>
       <c r="M96" s="3">
         <v>-60000</v>
       </c>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>-60000</v>
+      </c>
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3593,9 +3829,12 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3629,9 +3868,12 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3665,45 +3907,51 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-516300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-244600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-618300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-290300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-503200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-102800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>275800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-17300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>351000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>51200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>60600</v>
       </c>
-      <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3"/>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3731,49 +3979,55 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
       </c>
-      <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-30300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>6900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>11100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-8400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-18400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-17600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>13100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>7500</v>
       </c>
-      <c r="N102" s="3"/>
+      <c r="O102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
